--- a/test/Rappels pour participants lendemain-2023-10-18-16-10-36.xlsx
+++ b/test/Rappels pour participants lendemain-2023-10-18-16-10-36.xlsx
@@ -20,6 +20,7 @@
   <fonts count="8">
     <font>
       <name val="Arial"/>
+      <charset val="1"/>
       <family val="2"/>
       <sz val="10"/>
     </font>
@@ -271,7 +272,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -314,10 +318,10 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -790,1675 +794,1701 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:Z49"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.72265625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="4.33" customWidth="1" style="26" min="1" max="1"/>
-    <col width="23.01" customWidth="1" style="26" min="2" max="2"/>
-    <col width="44.99" customWidth="1" style="26" min="3" max="3"/>
-    <col width="8" customWidth="1" style="26" min="4" max="4"/>
-    <col width="13.01" customWidth="1" style="26" min="5" max="5"/>
-    <col width="23.01" customWidth="1" style="26" min="6" max="6"/>
-    <col width="16" customWidth="1" style="26" min="7" max="7"/>
-    <col width="36.99" customWidth="1" style="26" min="8" max="8"/>
-    <col width="23.01" customWidth="1" style="26" min="9" max="9"/>
-    <col width="18" customWidth="1" style="26" min="10" max="10"/>
-    <col width="19.99" customWidth="1" style="26" min="11" max="11"/>
-    <col width="177" customWidth="1" style="26" min="12" max="12"/>
-    <col width="4.33" customWidth="1" style="26" min="13" max="13"/>
+    <col width="4.33" customWidth="1" style="27" min="1" max="1"/>
+    <col width="23.01" customWidth="1" style="27" min="2" max="2"/>
+    <col width="44.99" customWidth="1" style="27" min="3" max="3"/>
+    <col width="8" customWidth="1" style="27" min="4" max="4"/>
+    <col width="13.02" customWidth="1" style="27" min="5" max="5"/>
+    <col width="23.01" customWidth="1" style="27" min="6" max="6"/>
+    <col width="16" customWidth="1" style="27" min="7" max="7"/>
+    <col width="36.99" customWidth="1" style="27" min="8" max="8"/>
+    <col width="23.01" customWidth="1" style="27" min="9" max="9"/>
+    <col width="18" customWidth="1" style="27" min="10" max="10"/>
+    <col width="19.99" customWidth="1" style="27" min="11" max="11"/>
+    <col width="177" customWidth="1" style="27" min="12" max="12"/>
+    <col width="4.33" customWidth="1" style="27" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="27">
-      <c r="A1" s="28" t="n"/>
-      <c r="B1" s="28" t="n"/>
-      <c r="C1" s="28" t="n"/>
-      <c r="D1" s="28" t="n"/>
-      <c r="E1" s="28" t="n"/>
-      <c r="F1" s="28" t="n"/>
-      <c r="G1" s="28" t="n"/>
-      <c r="H1" s="28" t="n"/>
-      <c r="I1" s="28" t="n"/>
-      <c r="J1" s="28" t="n"/>
-      <c r="K1" s="28" t="n"/>
-      <c r="L1" s="28" t="n"/>
-      <c r="M1" s="29" t="n"/>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="27">
-      <c r="A2" s="28" t="n"/>
-      <c r="B2" s="30" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="28">
+      <c r="A1" s="29" t="n"/>
+      <c r="B1" s="29" t="n"/>
+      <c r="C1" s="29" t="n"/>
+      <c r="D1" s="29" t="n"/>
+      <c r="E1" s="29" t="n"/>
+      <c r="F1" s="29" t="n"/>
+      <c r="G1" s="29" t="n"/>
+      <c r="H1" s="29" t="n"/>
+      <c r="I1" s="29" t="n"/>
+      <c r="J1" s="29" t="n"/>
+      <c r="K1" s="29" t="n"/>
+      <c r="L1" s="29" t="n"/>
+      <c r="M1" s="30" t="n"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="28">
+      <c r="A2" s="29" t="n"/>
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>Rappels pour participants lendemain</t>
         </is>
       </c>
-      <c r="C2" s="30" t="n"/>
-      <c r="D2" s="30" t="n"/>
-      <c r="E2" s="30" t="n"/>
-      <c r="F2" s="30" t="n"/>
-      <c r="G2" s="30" t="n"/>
-      <c r="H2" s="30" t="n"/>
-      <c r="I2" s="30" t="n"/>
-      <c r="J2" s="30" t="n"/>
-      <c r="K2" s="30" t="n"/>
-      <c r="L2" s="30" t="n"/>
-      <c r="M2" s="29" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="27">
-      <c r="A3" s="28" t="n"/>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="C2" s="31" t="n"/>
+      <c r="D2" s="31" t="n"/>
+      <c r="E2" s="31" t="n"/>
+      <c r="F2" s="31" t="n"/>
+      <c r="G2" s="31" t="n"/>
+      <c r="H2" s="31" t="n"/>
+      <c r="I2" s="31" t="n"/>
+      <c r="J2" s="31" t="n"/>
+      <c r="K2" s="31" t="n"/>
+      <c r="L2" s="31" t="n"/>
+      <c r="M2" s="30" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="28">
+      <c r="A3" s="29" t="n"/>
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>Au 2023-10-18 16:10:36 Heure d'Europe centrale/CET • Généré par Connect Lyon</t>
         </is>
       </c>
-      <c r="C3" s="31" t="n"/>
-      <c r="D3" s="31" t="n"/>
-      <c r="E3" s="31" t="n"/>
-      <c r="F3" s="31" t="n"/>
-      <c r="G3" s="31" t="n"/>
-      <c r="H3" s="31" t="n"/>
-      <c r="I3" s="31" t="n"/>
-      <c r="J3" s="31" t="n"/>
-      <c r="K3" s="31" t="n"/>
-      <c r="L3" s="31" t="n"/>
-      <c r="M3" s="29" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="27">
-      <c r="A4" s="32" t="n"/>
-      <c r="B4" s="32" t="n"/>
-      <c r="C4" s="32" t="n"/>
-      <c r="D4" s="32" t="n"/>
-      <c r="E4" s="32" t="n"/>
-      <c r="F4" s="32" t="n"/>
-      <c r="G4" s="32" t="n"/>
-      <c r="H4" s="32" t="n"/>
-      <c r="I4" s="32" t="n"/>
-      <c r="J4" s="32" t="n"/>
-      <c r="K4" s="32" t="n"/>
-      <c r="L4" s="32" t="n"/>
-      <c r="M4" s="33" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="27">
-      <c r="A5" s="34" t="n"/>
-      <c r="B5" s="34" t="n"/>
-      <c r="C5" s="34" t="n"/>
-      <c r="D5" s="34" t="n"/>
-      <c r="E5" s="34" t="n"/>
-      <c r="F5" s="34" t="n"/>
-      <c r="G5" s="34" t="n"/>
-      <c r="H5" s="34" t="n"/>
-      <c r="I5" s="34" t="n"/>
-      <c r="J5" s="34" t="n"/>
-      <c r="K5" s="34" t="n"/>
-      <c r="L5" s="34" t="n"/>
-      <c r="M5" s="35" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="27">
-      <c r="A6" s="34" t="n"/>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="C3" s="32" t="n"/>
+      <c r="D3" s="32" t="n"/>
+      <c r="E3" s="32" t="n"/>
+      <c r="F3" s="32" t="n"/>
+      <c r="G3" s="32" t="n"/>
+      <c r="H3" s="32" t="n"/>
+      <c r="I3" s="32" t="n"/>
+      <c r="J3" s="32" t="n"/>
+      <c r="K3" s="32" t="n"/>
+      <c r="L3" s="32" t="n"/>
+      <c r="M3" s="30" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="28">
+      <c r="A4" s="33" t="n"/>
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="33" t="n"/>
+      <c r="H4" s="33" t="n"/>
+      <c r="I4" s="33" t="n"/>
+      <c r="J4" s="33" t="n"/>
+      <c r="K4" s="33" t="n"/>
+      <c r="L4" s="33" t="n"/>
+      <c r="M4" s="34" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="28">
+      <c r="A5" s="35" t="n"/>
+      <c r="B5" s="35" t="n"/>
+      <c r="C5" s="35" t="n"/>
+      <c r="D5" s="35" t="n"/>
+      <c r="E5" s="35" t="n"/>
+      <c r="F5" s="35" t="n"/>
+      <c r="G5" s="35" t="n"/>
+      <c r="H5" s="35" t="n"/>
+      <c r="I5" s="35" t="n"/>
+      <c r="J5" s="35" t="n"/>
+      <c r="K5" s="35" t="n"/>
+      <c r="L5" s="35" t="n"/>
+      <c r="M5" s="36" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="28">
+      <c r="A6" s="35" t="n"/>
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Filtré par</t>
         </is>
       </c>
-      <c r="C6" s="36" t="n"/>
-      <c r="D6" s="36" t="n"/>
-      <c r="E6" s="36" t="n"/>
-      <c r="F6" s="36" t="n"/>
-      <c r="G6" s="36" t="n"/>
-      <c r="H6" s="36" t="n"/>
-      <c r="I6" s="36" t="n"/>
-      <c r="J6" s="36" t="n"/>
-      <c r="K6" s="36" t="n"/>
-      <c r="L6" s="36" t="n"/>
-      <c r="M6" s="35" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="27">
-      <c r="A7" s="34" t="n"/>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="C6" s="37" t="n"/>
+      <c r="D6" s="37" t="n"/>
+      <c r="E6" s="37" t="n"/>
+      <c r="F6" s="37" t="n"/>
+      <c r="G6" s="37" t="n"/>
+      <c r="H6" s="37" t="n"/>
+      <c r="I6" s="37" t="n"/>
+      <c r="J6" s="37" t="n"/>
+      <c r="K6" s="37" t="n"/>
+      <c r="L6" s="37" t="n"/>
+      <c r="M6" s="36" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="28">
+      <c r="A7" s="35" t="n"/>
+      <c r="B7" s="38" t="inlineStr">
         <is>
           <t>Afficher: Toutes les campagnes</t>
         </is>
       </c>
-      <c r="C7" s="37" t="n"/>
-      <c r="D7" s="37" t="n"/>
-      <c r="E7" s="37" t="n"/>
-      <c r="F7" s="37" t="n"/>
-      <c r="G7" s="37" t="n"/>
-      <c r="H7" s="37" t="n"/>
-      <c r="I7" s="37" t="n"/>
-      <c r="J7" s="37" t="n"/>
-      <c r="K7" s="37" t="n"/>
-      <c r="L7" s="37" t="n"/>
-      <c r="M7" s="35" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="27">
-      <c r="A8" s="34" t="n"/>
-      <c r="B8" s="37" t="n"/>
-      <c r="C8" s="37" t="n"/>
-      <c r="D8" s="37" t="n"/>
-      <c r="E8" s="37" t="n"/>
-      <c r="F8" s="37" t="n"/>
-      <c r="G8" s="37" t="n"/>
-      <c r="H8" s="37" t="n"/>
-      <c r="I8" s="37" t="n"/>
-      <c r="J8" s="37" t="n"/>
-      <c r="K8" s="37" t="n"/>
-      <c r="L8" s="37" t="n"/>
-      <c r="M8" s="35" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="27">
-      <c r="A9" s="34" t="n"/>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="38" t="n"/>
+      <c r="E7" s="38" t="n"/>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="38" t="n"/>
+      <c r="H7" s="38" t="n"/>
+      <c r="I7" s="38" t="n"/>
+      <c r="J7" s="38" t="n"/>
+      <c r="K7" s="38" t="n"/>
+      <c r="L7" s="38" t="n"/>
+      <c r="M7" s="36" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="28">
+      <c r="A8" s="35" t="n"/>
+      <c r="B8" s="38" t="n"/>
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="38" t="n"/>
+      <c r="E8" s="38" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="38" t="n"/>
+      <c r="H8" s="38" t="n"/>
+      <c r="I8" s="38" t="n"/>
+      <c r="J8" s="38" t="n"/>
+      <c r="K8" s="38" t="n"/>
+      <c r="L8" s="38" t="n"/>
+      <c r="M8" s="36" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="28">
+      <c r="A9" s="35" t="n"/>
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>Champ de date: Date &amp; Heure de début égal à Demain (19/10/2023 en 19/10/2023)</t>
         </is>
       </c>
-      <c r="C9" s="37" t="n"/>
-      <c r="D9" s="37" t="n"/>
-      <c r="E9" s="37" t="n"/>
-      <c r="F9" s="37" t="n"/>
-      <c r="G9" s="37" t="n"/>
-      <c r="H9" s="37" t="n"/>
-      <c r="I9" s="37" t="n"/>
-      <c r="J9" s="37" t="n"/>
-      <c r="K9" s="37" t="n"/>
-      <c r="L9" s="37" t="n"/>
-      <c r="M9" s="35" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="27">
-      <c r="A10" s="34" t="n"/>
-      <c r="B10" s="37" t="inlineStr">
+      <c r="C9" s="38" t="n"/>
+      <c r="D9" s="38" t="n"/>
+      <c r="E9" s="38" t="n"/>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="38" t="n"/>
+      <c r="H9" s="38" t="n"/>
+      <c r="I9" s="38" t="n"/>
+      <c r="J9" s="38" t="n"/>
+      <c r="K9" s="38" t="n"/>
+      <c r="L9" s="38" t="n"/>
+      <c r="M9" s="36" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="28">
+      <c r="A10" s="35" t="n"/>
+      <c r="B10" s="38" t="inlineStr">
         <is>
           <t>Statut égal à Planifiée</t>
         </is>
       </c>
-      <c r="C10" s="37" t="n"/>
-      <c r="D10" s="37" t="n"/>
-      <c r="E10" s="37" t="n"/>
-      <c r="F10" s="37" t="n"/>
-      <c r="G10" s="37" t="n"/>
-      <c r="H10" s="37" t="n"/>
-      <c r="I10" s="37" t="n"/>
-      <c r="J10" s="37" t="n"/>
-      <c r="K10" s="37" t="n"/>
-      <c r="L10" s="37" t="n"/>
-      <c r="M10" s="35" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="27">
-      <c r="A11" s="34" t="n"/>
-      <c r="B11" s="34" t="n"/>
-      <c r="C11" s="34" t="n"/>
-      <c r="D11" s="34" t="n"/>
-      <c r="E11" s="34" t="n"/>
-      <c r="F11" s="34" t="n"/>
-      <c r="G11" s="34" t="n"/>
-      <c r="H11" s="34" t="n"/>
-      <c r="I11" s="34" t="n"/>
-      <c r="J11" s="34" t="n"/>
-      <c r="K11" s="34" t="n"/>
-      <c r="L11" s="34" t="n"/>
-      <c r="M11" s="35" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="27">
-      <c r="A12" s="34" t="n"/>
-      <c r="B12" s="38" t="inlineStr">
+      <c r="C10" s="38" t="n"/>
+      <c r="D10" s="38" t="n"/>
+      <c r="E10" s="38" t="n"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="38" t="n"/>
+      <c r="H10" s="38" t="n"/>
+      <c r="I10" s="38" t="n"/>
+      <c r="J10" s="38" t="n"/>
+      <c r="K10" s="38" t="n"/>
+      <c r="L10" s="38" t="n"/>
+      <c r="M10" s="36" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="28">
+      <c r="A11" s="35" t="n"/>
+      <c r="B11" s="35" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="35" t="n"/>
+      <c r="G11" s="35" t="n"/>
+      <c r="H11" s="35" t="n"/>
+      <c r="I11" s="35" t="n"/>
+      <c r="J11" s="35" t="n"/>
+      <c r="K11" s="35" t="n"/>
+      <c r="L11" s="35" t="n"/>
+      <c r="M11" s="36" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="28">
+      <c r="A12" s="35" t="n"/>
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>Nom de la campagne  ↑</t>
         </is>
       </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="C12" s="39" t="inlineStr">
         <is>
           <t>Nom de l'activité  ↑</t>
         </is>
       </c>
-      <c r="D12" s="39" t="n"/>
-      <c r="E12" s="38" t="inlineStr">
+      <c r="D12" s="40" t="n"/>
+      <c r="E12" s="39" t="inlineStr">
         <is>
           <t>Type de RDV</t>
         </is>
       </c>
-      <c r="F12" s="38" t="inlineStr">
+      <c r="F12" s="39" t="inlineStr">
         <is>
           <t>Date &amp; Heure de début</t>
         </is>
       </c>
-      <c r="G12" s="38" t="inlineStr">
+      <c r="G12" s="39" t="inlineStr">
         <is>
           <t>N° Participant</t>
         </is>
       </c>
-      <c r="H12" s="38" t="inlineStr">
+      <c r="H12" s="39" t="inlineStr">
         <is>
           <t>Nom complet</t>
         </is>
       </c>
-      <c r="I12" s="38" t="inlineStr">
+      <c r="I12" s="39" t="inlineStr">
         <is>
           <t>Numéro à appeler</t>
         </is>
       </c>
-      <c r="J12" s="38" t="inlineStr">
+      <c r="J12" s="39" t="inlineStr">
         <is>
           <t>Statut de rappel</t>
         </is>
       </c>
-      <c r="K12" s="38" t="inlineStr">
+      <c r="K12" s="39" t="inlineStr">
         <is>
           <t>Statut participant</t>
         </is>
       </c>
-      <c r="L12" s="38" t="inlineStr">
+      <c r="L12" s="39" t="inlineStr">
         <is>
           <t>Observations</t>
         </is>
       </c>
-      <c r="M12" s="35" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="27">
-      <c r="A13" s="34" t="n"/>
-      <c r="B13" s="40" t="inlineStr">
+      <c r="M12" s="36" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="28">
+      <c r="A13" s="35" t="n"/>
+      <c r="B13" s="41" t="inlineStr">
         <is>
           <t>Bénévolat - Lyon</t>
         </is>
       </c>
-      <c r="C13" s="40" t="inlineStr">
+      <c r="C13" s="41" t="inlineStr">
         <is>
           <t>Parcours senior - CCAS Décines</t>
         </is>
       </c>
-      <c r="D13" s="41" t="n"/>
-      <c r="E13" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F13" s="42" t="inlineStr">
+      <c r="D13" s="42" t="n"/>
+      <c r="E13" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F13" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 14:00</t>
         </is>
       </c>
-      <c r="G13" s="42" t="inlineStr">
+      <c r="G13" s="43" t="inlineStr">
         <is>
           <t>P-101838</t>
         </is>
       </c>
-      <c r="H13" s="42" t="inlineStr">
+      <c r="H13" s="43" t="inlineStr">
         <is>
           <t>Malika ABER AOUNI</t>
         </is>
       </c>
-      <c r="I13" s="42" t="n"/>
-      <c r="J13" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K13" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L13" s="42" t="n"/>
-      <c r="M13" s="35" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="27">
-      <c r="A14" s="34" t="n"/>
-      <c r="B14" s="43" t="n"/>
-      <c r="C14" s="43" t="n"/>
-      <c r="D14" s="44" t="n"/>
-      <c r="E14" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F14" s="42" t="inlineStr">
+      <c r="I13" s="43" t="n"/>
+      <c r="J13" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K13" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L13" s="43" t="n"/>
+      <c r="M13" s="36" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="28">
+      <c r="A14" s="35" t="n"/>
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="45" t="n"/>
+      <c r="E14" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F14" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 14:00</t>
         </is>
       </c>
-      <c r="G14" s="42" t="inlineStr">
+      <c r="G14" s="43" t="inlineStr">
         <is>
           <t>P-104937</t>
         </is>
       </c>
-      <c r="H14" s="42" t="inlineStr">
+      <c r="H14" s="43" t="inlineStr">
         <is>
           <t>Angéline GUILLET</t>
         </is>
       </c>
-      <c r="I14" s="42" t="n"/>
-      <c r="J14" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K14" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L14" s="42" t="n"/>
-      <c r="M14" s="35" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="27">
-      <c r="A15" s="34" t="n"/>
-      <c r="B15" s="43" t="n"/>
-      <c r="C15" s="43" t="n"/>
-      <c r="D15" s="44" t="n"/>
-      <c r="E15" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F15" s="42" t="inlineStr">
+      <c r="I14" s="43" t="n"/>
+      <c r="J14" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K14" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L14" s="43" t="n"/>
+      <c r="M14" s="36" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="28">
+      <c r="A15" s="35" t="n"/>
+      <c r="B15" s="44" t="n"/>
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="45" t="n"/>
+      <c r="E15" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F15" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 14:00</t>
         </is>
       </c>
-      <c r="G15" s="42" t="inlineStr">
+      <c r="G15" s="43" t="inlineStr">
         <is>
           <t>P-104952</t>
         </is>
       </c>
-      <c r="H15" s="42" t="inlineStr">
+      <c r="H15" s="43" t="inlineStr">
         <is>
           <t>Nersis HRABIDIAN</t>
         </is>
       </c>
-      <c r="I15" s="42" t="n"/>
-      <c r="J15" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K15" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L15" s="42" t="n"/>
-      <c r="M15" s="35" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="27">
-      <c r="A16" s="34" t="n"/>
-      <c r="B16" s="43" t="n"/>
-      <c r="C16" s="43" t="n"/>
-      <c r="D16" s="44" t="n"/>
-      <c r="E16" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F16" s="42" t="inlineStr">
+      <c r="I15" s="43" t="n"/>
+      <c r="J15" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K15" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L15" s="43" t="n"/>
+      <c r="M15" s="36" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="28">
+      <c r="A16" s="35" t="n"/>
+      <c r="B16" s="44" t="n"/>
+      <c r="C16" s="44" t="n"/>
+      <c r="D16" s="45" t="n"/>
+      <c r="E16" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F16" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 14:00</t>
         </is>
       </c>
-      <c r="G16" s="42" t="inlineStr">
+      <c r="G16" s="43" t="inlineStr">
         <is>
           <t>P-104967</t>
         </is>
       </c>
-      <c r="H16" s="42" t="inlineStr">
+      <c r="H16" s="43" t="inlineStr">
         <is>
           <t>Mourad GHEDIRI</t>
         </is>
       </c>
-      <c r="I16" s="42" t="n"/>
-      <c r="J16" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K16" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L16" s="42" t="n"/>
-      <c r="M16" s="35" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="27">
-      <c r="A17" s="34" t="n"/>
-      <c r="B17" s="43" t="n"/>
-      <c r="C17" s="43" t="n"/>
-      <c r="D17" s="44" t="n"/>
-      <c r="E17" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F17" s="42" t="inlineStr">
+      <c r="I16" s="43" t="n"/>
+      <c r="J16" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K16" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L16" s="43" t="n"/>
+      <c r="M16" s="36" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="28">
+      <c r="A17" s="35" t="n"/>
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="44" t="n"/>
+      <c r="D17" s="45" t="n"/>
+      <c r="E17" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F17" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 14:00</t>
         </is>
       </c>
-      <c r="G17" s="42" t="inlineStr">
+      <c r="G17" s="43" t="inlineStr">
         <is>
           <t>P-104982</t>
         </is>
       </c>
-      <c r="H17" s="42" t="inlineStr">
+      <c r="H17" s="43" t="inlineStr">
         <is>
           <t>Evelyne JARRY</t>
         </is>
       </c>
-      <c r="I17" s="42" t="n"/>
-      <c r="J17" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K17" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L17" s="42" t="n"/>
-      <c r="M17" s="35" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="27">
-      <c r="A18" s="34" t="n"/>
-      <c r="B18" s="43" t="n"/>
-      <c r="C18" s="43" t="n"/>
-      <c r="D18" s="44" t="n"/>
-      <c r="E18" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F18" s="42" t="inlineStr">
+      <c r="I17" s="43" t="n"/>
+      <c r="J17" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K17" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L17" s="43" t="n"/>
+      <c r="M17" s="36" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="28">
+      <c r="A18" s="35" t="n"/>
+      <c r="B18" s="44" t="n"/>
+      <c r="C18" s="44" t="n"/>
+      <c r="D18" s="45" t="n"/>
+      <c r="E18" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F18" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 14:00</t>
         </is>
       </c>
-      <c r="G18" s="42" t="inlineStr">
+      <c r="G18" s="43" t="inlineStr">
         <is>
           <t>P-104997</t>
         </is>
       </c>
-      <c r="H18" s="42" t="inlineStr">
+      <c r="H18" s="43" t="inlineStr">
         <is>
           <t>Brigitte DAVIN</t>
         </is>
       </c>
-      <c r="I18" s="42" t="n"/>
-      <c r="J18" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K18" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L18" s="42" t="n"/>
-      <c r="M18" s="35" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="27">
-      <c r="A19" s="34" t="n"/>
-      <c r="B19" s="43" t="n"/>
-      <c r="C19" s="40" t="inlineStr">
+      <c r="I18" s="43" t="n"/>
+      <c r="J18" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K18" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L18" s="43" t="n"/>
+      <c r="M18" s="36" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="28">
+      <c r="A19" s="35" t="n"/>
+      <c r="B19" s="44" t="n"/>
+      <c r="C19" s="41" t="inlineStr">
         <is>
           <t>Parcours senior - Un moment de détente 2023</t>
         </is>
       </c>
-      <c r="D19" s="41" t="n"/>
-      <c r="E19" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F19" s="42" t="inlineStr">
+      <c r="D19" s="42" t="n"/>
+      <c r="E19" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F19" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 09:30</t>
         </is>
       </c>
-      <c r="G19" s="42" t="inlineStr">
+      <c r="G19" s="43" t="inlineStr">
         <is>
           <t>P-111215</t>
         </is>
       </c>
-      <c r="H19" s="42" t="inlineStr">
+      <c r="H19" s="43" t="inlineStr">
         <is>
           <t>Jacqueline PSALTOPOULOS</t>
         </is>
       </c>
-      <c r="I19" s="42" t="n"/>
-      <c r="J19" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K19" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L19" s="42" t="n"/>
-      <c r="M19" s="35" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="27">
-      <c r="A20" s="34" t="n"/>
-      <c r="B20" s="43" t="n"/>
-      <c r="C20" s="43" t="n"/>
-      <c r="D20" s="44" t="n"/>
-      <c r="E20" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F20" s="42" t="inlineStr">
+      <c r="I19" s="43" t="n"/>
+      <c r="J19" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K19" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L19" s="43" t="n"/>
+      <c r="M19" s="36" t="n"/>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="28">
+      <c r="A20" s="35" t="n"/>
+      <c r="B20" s="44" t="n"/>
+      <c r="C20" s="44" t="n"/>
+      <c r="D20" s="45" t="n"/>
+      <c r="E20" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F20" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 09:30</t>
         </is>
       </c>
-      <c r="G20" s="42" t="inlineStr">
+      <c r="G20" s="43" t="inlineStr">
         <is>
           <t>P-111229</t>
         </is>
       </c>
-      <c r="H20" s="42" t="inlineStr">
+      <c r="H20" s="43" t="inlineStr">
         <is>
           <t>Annick GAUTHIER</t>
         </is>
       </c>
-      <c r="I20" s="42" t="n"/>
-      <c r="J20" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K20" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L20" s="42" t="n"/>
-      <c r="M20" s="35" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="27">
-      <c r="A21" s="34" t="n"/>
-      <c r="B21" s="43" t="n"/>
-      <c r="C21" s="43" t="n"/>
-      <c r="D21" s="44" t="n"/>
-      <c r="E21" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F21" s="42" t="inlineStr">
+      <c r="I20" s="43" t="n"/>
+      <c r="J20" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K20" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L20" s="43" t="n"/>
+      <c r="M20" s="36" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="28">
+      <c r="A21" s="35" t="n"/>
+      <c r="B21" s="44" t="n"/>
+      <c r="C21" s="44" t="n"/>
+      <c r="D21" s="45" t="n"/>
+      <c r="E21" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F21" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 09:30</t>
         </is>
       </c>
-      <c r="G21" s="42" t="inlineStr">
+      <c r="G21" s="43" t="inlineStr">
         <is>
           <t>P-111243</t>
         </is>
       </c>
-      <c r="H21" s="42" t="inlineStr">
+      <c r="H21" s="43" t="inlineStr">
         <is>
           <t>Chantal ESCOFFIER</t>
         </is>
       </c>
-      <c r="I21" s="42" t="n"/>
-      <c r="J21" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K21" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L21" s="42" t="n"/>
-      <c r="M21" s="35" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="27">
-      <c r="A22" s="34" t="n"/>
-      <c r="B22" s="43" t="n"/>
-      <c r="C22" s="43" t="n"/>
-      <c r="D22" s="44" t="n"/>
-      <c r="E22" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F22" s="42" t="inlineStr">
+      <c r="I21" s="43" t="n"/>
+      <c r="J21" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K21" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L21" s="43" t="n"/>
+      <c r="M21" s="36" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="28">
+      <c r="A22" s="35" t="n"/>
+      <c r="B22" s="44" t="n"/>
+      <c r="C22" s="44" t="n"/>
+      <c r="D22" s="45" t="n"/>
+      <c r="E22" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F22" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 09:30</t>
         </is>
       </c>
-      <c r="G22" s="42" t="inlineStr">
+      <c r="G22" s="43" t="inlineStr">
         <is>
           <t>P-111257</t>
         </is>
       </c>
-      <c r="H22" s="42" t="inlineStr">
+      <c r="H22" s="43" t="inlineStr">
         <is>
           <t>Lucie DELL'OLIO</t>
         </is>
       </c>
-      <c r="I22" s="42" t="n"/>
-      <c r="J22" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K22" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L22" s="42" t="n"/>
-      <c r="M22" s="35" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="27">
-      <c r="A23" s="34" t="n"/>
-      <c r="B23" s="43" t="n"/>
-      <c r="C23" s="43" t="n"/>
-      <c r="D23" s="44" t="n"/>
-      <c r="E23" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F23" s="42" t="inlineStr">
+      <c r="I22" s="43" t="n"/>
+      <c r="J22" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K22" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L22" s="43" t="n"/>
+      <c r="M22" s="36" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="28">
+      <c r="A23" s="35" t="n"/>
+      <c r="B23" s="44" t="n"/>
+      <c r="C23" s="44" t="n"/>
+      <c r="D23" s="45" t="n"/>
+      <c r="E23" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F23" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 09:30</t>
         </is>
       </c>
-      <c r="G23" s="42" t="inlineStr">
+      <c r="G23" s="43" t="inlineStr">
         <is>
           <t>P-111271</t>
         </is>
       </c>
-      <c r="H23" s="42" t="inlineStr">
+      <c r="H23" s="43" t="inlineStr">
         <is>
           <t>Sacha DUJARDIN</t>
         </is>
       </c>
-      <c r="I23" s="42" t="n"/>
-      <c r="J23" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K23" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L23" s="42" t="n"/>
-      <c r="M23" s="35" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="27">
-      <c r="A24" s="34" t="n"/>
-      <c r="B24" s="43" t="n"/>
-      <c r="C24" s="40" t="inlineStr">
+      <c r="I23" s="43" t="n"/>
+      <c r="J23" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K23" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L23" s="43" t="n"/>
+      <c r="M23" s="36" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="28">
+      <c r="A24" s="35" t="n"/>
+      <c r="B24" s="44" t="n"/>
+      <c r="C24" s="41" t="inlineStr">
         <is>
           <t>Permanence Connectée</t>
         </is>
       </c>
-      <c r="D24" s="41" t="n"/>
-      <c r="E24" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F24" s="42" t="inlineStr">
+      <c r="D24" s="42" t="n"/>
+      <c r="E24" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F24" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 14:15</t>
         </is>
       </c>
-      <c r="G24" s="42" t="inlineStr">
+      <c r="G24" s="43" t="inlineStr">
         <is>
           <t>P-110831</t>
         </is>
       </c>
-      <c r="H24" s="42" t="inlineStr">
+      <c r="H24" s="43" t="inlineStr">
         <is>
           <t>Musette MASIKA</t>
         </is>
       </c>
-      <c r="I24" s="42" t="inlineStr">
+      <c r="I24" s="43" t="inlineStr">
         <is>
           <t>07 60 40 56 98</t>
         </is>
       </c>
-      <c r="J24" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K24" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L24" s="42" t="n"/>
-      <c r="M24" s="35" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="27">
-      <c r="A25" s="34" t="n"/>
-      <c r="B25" s="43" t="n"/>
-      <c r="C25" s="43" t="n"/>
-      <c r="D25" s="44" t="n"/>
-      <c r="E25" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F25" s="42" t="inlineStr">
+      <c r="J24" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K24" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L24" s="43" t="n"/>
+      <c r="M24" s="36" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="28">
+      <c r="A25" s="35" t="n"/>
+      <c r="B25" s="44" t="n"/>
+      <c r="C25" s="44" t="n"/>
+      <c r="D25" s="45" t="n"/>
+      <c r="E25" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F25" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 14:15</t>
         </is>
       </c>
-      <c r="G25" s="42" t="inlineStr">
+      <c r="G25" s="43" t="inlineStr">
         <is>
           <t>P-110895</t>
         </is>
       </c>
-      <c r="H25" s="42" t="inlineStr">
+      <c r="H25" s="43" t="inlineStr">
         <is>
           <t>Anfoua ANKIDINE</t>
         </is>
       </c>
-      <c r="I25" s="42" t="inlineStr">
+      <c r="I25" s="43" t="inlineStr">
         <is>
           <t>07 60 40 56 98</t>
         </is>
       </c>
-      <c r="J25" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K25" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L25" s="42" t="n"/>
-      <c r="M25" s="35" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="27">
-      <c r="A26" s="34" t="n"/>
-      <c r="B26" s="43" t="n"/>
-      <c r="C26" s="43" t="n"/>
-      <c r="D26" s="44" t="n"/>
-      <c r="E26" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F26" s="42" t="inlineStr">
+      <c r="J25" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K25" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L25" s="43" t="n"/>
+      <c r="M25" s="36" t="n"/>
+      <c r="Z25" s="27">
+        <f>TRUE()</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="28">
+      <c r="A26" s="35" t="n"/>
+      <c r="B26" s="44" t="n"/>
+      <c r="C26" s="44" t="n"/>
+      <c r="D26" s="45" t="n"/>
+      <c r="E26" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F26" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 14:15</t>
         </is>
       </c>
-      <c r="G26" s="42" t="inlineStr">
+      <c r="G26" s="43" t="inlineStr">
         <is>
           <t>P-110967</t>
         </is>
       </c>
-      <c r="H26" s="42" t="inlineStr">
+      <c r="H26" s="43" t="inlineStr">
         <is>
           <t>Brigitte MBONIGABA</t>
         </is>
       </c>
-      <c r="I26" s="42" t="inlineStr">
-        <is>
-          <t>07.69.96.89.27</t>
-        </is>
-      </c>
-      <c r="J26" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K26" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L26" s="42" t="n"/>
-      <c r="M26" s="35" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="27">
-      <c r="A27" s="34" t="n"/>
-      <c r="B27" s="43" t="n"/>
-      <c r="C27" s="43" t="n"/>
-      <c r="D27" s="44" t="n"/>
-      <c r="E27" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F27" s="42" t="inlineStr">
+      <c r="I26" s="43" t="inlineStr">
+        <is>
+          <t>07 60 40 56 98</t>
+        </is>
+      </c>
+      <c r="J26" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K26" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L26" s="43" t="n"/>
+      <c r="M26" s="36" t="n"/>
+      <c r="Z26" s="27" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="28">
+      <c r="A27" s="35" t="n"/>
+      <c r="B27" s="44" t="n"/>
+      <c r="C27" s="44" t="n"/>
+      <c r="D27" s="45" t="n"/>
+      <c r="E27" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F27" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 14:15</t>
         </is>
       </c>
-      <c r="G27" s="42" t="inlineStr">
+      <c r="G27" s="43" t="inlineStr">
         <is>
           <t>P-112843</t>
         </is>
       </c>
-      <c r="H27" s="42" t="inlineStr">
+      <c r="H27" s="43" t="inlineStr">
         <is>
           <t>Abdelmadjid MEZOUAR</t>
         </is>
       </c>
-      <c r="I27" s="42" t="inlineStr">
-        <is>
-          <t>0644912307</t>
-        </is>
-      </c>
-      <c r="J27" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K27" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L27" s="42" t="n"/>
-      <c r="M27" s="35" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="27">
-      <c r="A28" s="34" t="n"/>
-      <c r="B28" s="43" t="n"/>
-      <c r="C28" s="43" t="n"/>
-      <c r="D28" s="44" t="n"/>
-      <c r="E28" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F28" s="42" t="inlineStr">
+      <c r="I27" s="43" t="inlineStr">
+        <is>
+          <t>760405698</t>
+        </is>
+      </c>
+      <c r="J27" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K27" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L27" s="43" t="n"/>
+      <c r="M27" s="36" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="28">
+      <c r="A28" s="35" t="n"/>
+      <c r="B28" s="44" t="n"/>
+      <c r="C28" s="44" t="n"/>
+      <c r="D28" s="45" t="n"/>
+      <c r="E28" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F28" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 16:00</t>
         </is>
       </c>
-      <c r="G28" s="42" t="inlineStr">
+      <c r="G28" s="43" t="inlineStr">
         <is>
           <t>P-110850</t>
         </is>
       </c>
-      <c r="H28" s="42" t="inlineStr">
+      <c r="H28" s="43" t="inlineStr">
         <is>
           <t>Mohammed MEDDAHI</t>
         </is>
       </c>
-      <c r="I28" s="42" t="inlineStr">
-        <is>
-          <t>0610172974</t>
-        </is>
-      </c>
-      <c r="J28" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K28" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L28" s="42" t="n"/>
-      <c r="M28" s="35" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="27">
-      <c r="A29" s="34" t="n"/>
-      <c r="B29" s="43" t="n"/>
-      <c r="C29" s="43" t="n"/>
-      <c r="D29" s="44" t="n"/>
-      <c r="E29" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F29" s="42" t="inlineStr">
+      <c r="I28" s="43" t="n">
+        <v>760405698</v>
+      </c>
+      <c r="J28" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K28" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L28" s="43" t="n"/>
+      <c r="M28" s="36" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="28">
+      <c r="A29" s="35" t="n"/>
+      <c r="B29" s="44" t="n"/>
+      <c r="C29" s="44" t="n"/>
+      <c r="D29" s="45" t="n"/>
+      <c r="E29" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F29" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 16:00</t>
         </is>
       </c>
-      <c r="G29" s="42" t="inlineStr">
+      <c r="G29" s="43" t="inlineStr">
         <is>
           <t>P-111034</t>
         </is>
       </c>
-      <c r="H29" s="42" t="inlineStr">
+      <c r="H29" s="43" t="inlineStr">
         <is>
           <t>Abdoulaye Pathé DIALLO</t>
         </is>
       </c>
-      <c r="I29" s="42" t="inlineStr">
+      <c r="I29" s="43" t="inlineStr">
         <is>
           <t>0760405698</t>
         </is>
       </c>
-      <c r="J29" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K29" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L29" s="42" t="n"/>
-      <c r="M29" s="35" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="27">
-      <c r="A30" s="34" t="n"/>
-      <c r="B30" s="43" t="n"/>
-      <c r="C30" s="43" t="n"/>
-      <c r="D30" s="44" t="n"/>
-      <c r="E30" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F30" s="42" t="inlineStr">
+      <c r="J29" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K29" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L29" s="43" t="n"/>
+      <c r="M29" s="36" t="n"/>
+      <c r="Z29" s="27" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="28">
+      <c r="A30" s="35" t="n"/>
+      <c r="B30" s="44" t="n"/>
+      <c r="C30" s="44" t="n"/>
+      <c r="D30" s="45" t="n"/>
+      <c r="E30" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F30" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 16:00</t>
         </is>
       </c>
-      <c r="G30" s="42" t="inlineStr">
+      <c r="G30" s="43" t="inlineStr">
         <is>
           <t>P-111212</t>
         </is>
       </c>
-      <c r="H30" s="42" t="inlineStr">
+      <c r="H30" s="43" t="inlineStr">
         <is>
           <t>Etse Ameli GAGAH</t>
         </is>
       </c>
-      <c r="I30" s="42" t="inlineStr">
+      <c r="I30" s="43" t="inlineStr">
         <is>
           <t>07 60 40 56 98</t>
         </is>
       </c>
-      <c r="J30" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K30" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L30" s="42" t="n"/>
-      <c r="M30" s="35" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="27">
-      <c r="A31" s="34" t="n"/>
-      <c r="B31" s="43" t="n"/>
-      <c r="C31" s="43" t="n"/>
-      <c r="D31" s="44" t="n"/>
-      <c r="E31" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F31" s="42" t="inlineStr">
+      <c r="J30" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K30" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L30" s="43" t="n"/>
+      <c r="M30" s="36" t="n"/>
+      <c r="Z30" s="27" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="28">
+      <c r="A31" s="35" t="n"/>
+      <c r="B31" s="44" t="n"/>
+      <c r="C31" s="44" t="n"/>
+      <c r="D31" s="45" t="n"/>
+      <c r="E31" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F31" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 16:00</t>
         </is>
       </c>
-      <c r="G31" s="42" t="inlineStr">
+      <c r="G31" s="43" t="inlineStr">
         <is>
           <t>P-112813</t>
         </is>
       </c>
-      <c r="H31" s="42" t="inlineStr">
+      <c r="H31" s="43" t="inlineStr">
         <is>
           <t>TSHIJIKA MARGUERITE MUSENGA (APTIC)</t>
         </is>
       </c>
-      <c r="I31" s="42" t="inlineStr">
-        <is>
-          <t>0758000603</t>
-        </is>
-      </c>
-      <c r="J31" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K31" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L31" s="42" t="n"/>
-      <c r="M31" s="35" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="27">
-      <c r="A32" s="34" t="n"/>
-      <c r="B32" s="40" t="inlineStr">
+      <c r="I31" s="43" t="n">
+        <v>76040569800</v>
+      </c>
+      <c r="J31" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K31" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L31" s="43" t="n"/>
+      <c r="M31" s="36" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="28">
+      <c r="A32" s="35" t="n"/>
+      <c r="B32" s="41" t="inlineStr">
         <is>
           <t>RDV - Lyon</t>
         </is>
       </c>
-      <c r="C32" s="40" t="inlineStr">
+      <c r="C32" s="41" t="inlineStr">
         <is>
           <t>RDV bénéficiaire</t>
         </is>
       </c>
-      <c r="D32" s="41" t="n"/>
-      <c r="E32" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F32" s="42" t="inlineStr">
+      <c r="D32" s="42" t="n"/>
+      <c r="E32" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F32" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 09:30</t>
         </is>
       </c>
-      <c r="G32" s="42" t="inlineStr">
+      <c r="G32" s="43" t="inlineStr">
         <is>
           <t>P-109490</t>
         </is>
       </c>
-      <c r="H32" s="42" t="inlineStr">
+      <c r="H32" s="43" t="inlineStr">
         <is>
           <t>Ayele KPOGNON</t>
         </is>
       </c>
-      <c r="I32" s="42" t="inlineStr">
+      <c r="I32" s="43" t="inlineStr">
         <is>
           <t>0782716250</t>
         </is>
       </c>
-      <c r="J32" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K32" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L32" s="42" t="n"/>
-      <c r="M32" s="35" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="27">
-      <c r="A33" s="34" t="n"/>
-      <c r="B33" s="43" t="n"/>
-      <c r="C33" s="43" t="n"/>
-      <c r="D33" s="44" t="n"/>
-      <c r="E33" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F33" s="42" t="inlineStr">
+      <c r="J32" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K32" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L32" s="43" t="n"/>
+      <c r="M32" s="36" t="n"/>
+      <c r="Z32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="28">
+      <c r="A33" s="35" t="n"/>
+      <c r="B33" s="44" t="n"/>
+      <c r="C33" s="44" t="n"/>
+      <c r="D33" s="45" t="n"/>
+      <c r="E33" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F33" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 10:00</t>
         </is>
       </c>
-      <c r="G33" s="42" t="inlineStr">
+      <c r="G33" s="43" t="inlineStr">
         <is>
           <t>P-108952</t>
         </is>
       </c>
-      <c r="H33" s="42" t="inlineStr">
+      <c r="H33" s="43" t="inlineStr">
         <is>
           <t>Azharqui AL HANDOO</t>
         </is>
       </c>
-      <c r="I33" s="42" t="inlineStr">
+      <c r="I33" s="43" t="inlineStr">
         <is>
           <t>06 66 63 59 14</t>
         </is>
       </c>
-      <c r="J33" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K33" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L33" s="42" t="n"/>
-      <c r="M33" s="35" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="27">
-      <c r="A34" s="34" t="n"/>
-      <c r="B34" s="43" t="n"/>
-      <c r="C34" s="43" t="n"/>
-      <c r="D34" s="44" t="n"/>
-      <c r="E34" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F34" s="42" t="inlineStr">
+      <c r="J33" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K33" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L33" s="43" t="n"/>
+      <c r="M33" s="36" t="n"/>
+      <c r="Z33" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="28">
+      <c r="A34" s="35" t="n"/>
+      <c r="B34" s="44" t="n"/>
+      <c r="C34" s="44" t="n"/>
+      <c r="D34" s="45" t="n"/>
+      <c r="E34" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F34" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 10:30</t>
         </is>
       </c>
-      <c r="G34" s="42" t="inlineStr">
+      <c r="G34" s="43" t="inlineStr">
         <is>
           <t>P-110391</t>
         </is>
       </c>
-      <c r="H34" s="42" t="inlineStr">
+      <c r="H34" s="43" t="inlineStr">
         <is>
           <t>Latra NEMER</t>
         </is>
       </c>
-      <c r="I34" s="42" t="inlineStr">
+      <c r="I34" s="43" t="inlineStr">
         <is>
           <t>0695312271</t>
         </is>
       </c>
-      <c r="J34" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K34" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L34" s="42" t="inlineStr">
+      <c r="J34" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K34" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L34" s="43" t="inlineStr">
         <is>
           <t>Apprenante sur le parcours parentalité Médialys (donc fiche Salesforce existante mais incomplète)</t>
         </is>
       </c>
-      <c r="M34" s="35" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="27">
-      <c r="A35" s="34" t="n"/>
-      <c r="B35" s="43" t="n"/>
-      <c r="C35" s="43" t="n"/>
-      <c r="D35" s="44" t="n"/>
-      <c r="E35" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F35" s="42" t="inlineStr">
+      <c r="M34" s="36" t="n"/>
+      <c r="Z34" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="28">
+      <c r="A35" s="35" t="n"/>
+      <c r="B35" s="44" t="n"/>
+      <c r="C35" s="44" t="n"/>
+      <c r="D35" s="45" t="n"/>
+      <c r="E35" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F35" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 11:00</t>
         </is>
       </c>
-      <c r="G35" s="42" t="inlineStr">
+      <c r="G35" s="43" t="inlineStr">
         <is>
           <t>P-110846</t>
         </is>
       </c>
-      <c r="H35" s="42" t="inlineStr">
+      <c r="H35" s="43" t="inlineStr">
         <is>
           <t>Raissa GUEHRIA</t>
         </is>
       </c>
-      <c r="I35" s="42" t="inlineStr">
-        <is>
-          <t>0768922321</t>
-        </is>
-      </c>
-      <c r="J35" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K35" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L35" s="42" t="inlineStr">
+      <c r="I35" s="43" t="inlineStr">
+        <is>
+          <t>076892232</t>
+        </is>
+      </c>
+      <c r="J35" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K35" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L35" s="43" t="inlineStr">
         <is>
           <t>Il s'agira de la soeur de Madame GUEHRIA, celle -ci ayant cours et n'étant pas disponible. Sa soeur viendra faire son inscription donc, et prendre un rdv vente pc si possible.</t>
         </is>
       </c>
-      <c r="M35" s="35" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="27">
-      <c r="A36" s="34" t="n"/>
-      <c r="B36" s="43" t="n"/>
-      <c r="C36" s="43" t="n"/>
-      <c r="D36" s="44" t="n"/>
-      <c r="E36" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F36" s="42" t="inlineStr">
+      <c r="M35" s="36" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="28">
+      <c r="A36" s="35" t="n"/>
+      <c r="B36" s="44" t="n"/>
+      <c r="C36" s="44" t="n"/>
+      <c r="D36" s="45" t="n"/>
+      <c r="E36" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F36" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 12:00</t>
         </is>
       </c>
-      <c r="G36" s="42" t="inlineStr">
+      <c r="G36" s="43" t="inlineStr">
         <is>
           <t>P-110941</t>
         </is>
       </c>
-      <c r="H36" s="42" t="inlineStr">
+      <c r="H36" s="43" t="inlineStr">
         <is>
           <t>Ashot SETRAKYAN</t>
         </is>
       </c>
-      <c r="I36" s="42" t="inlineStr">
+      <c r="I36" s="43" t="inlineStr">
         <is>
           <t>0766348484</t>
         </is>
       </c>
-      <c r="J36" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K36" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L36" s="42" t="n"/>
-      <c r="M36" s="35" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="27">
-      <c r="A37" s="34" t="n"/>
-      <c r="B37" s="43" t="n"/>
-      <c r="C37" s="43" t="n"/>
-      <c r="D37" s="44" t="n"/>
-      <c r="E37" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F37" s="42" t="inlineStr">
+      <c r="J36" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K36" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L36" s="43" t="n"/>
+      <c r="M36" s="36" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="28">
+      <c r="A37" s="35" t="n"/>
+      <c r="B37" s="44" t="n"/>
+      <c r="C37" s="44" t="n"/>
+      <c r="D37" s="45" t="n"/>
+      <c r="E37" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F37" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 11:30</t>
         </is>
       </c>
-      <c r="G37" s="42" t="inlineStr">
+      <c r="G37" s="43" t="inlineStr">
         <is>
           <t>P-109574</t>
         </is>
       </c>
-      <c r="H37" s="42" t="inlineStr">
+      <c r="H37" s="43" t="inlineStr">
         <is>
           <t>Guy NGAHANA</t>
         </is>
       </c>
-      <c r="I37" s="42" t="inlineStr">
-        <is>
-          <t>0605753947</t>
-        </is>
-      </c>
-      <c r="J37" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K37" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L37" s="42" t="n"/>
-      <c r="M37" s="35" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="27">
-      <c r="A38" s="34" t="n"/>
-      <c r="B38" s="43" t="n"/>
-      <c r="C38" s="43" t="n"/>
-      <c r="D38" s="44" t="n"/>
-      <c r="E38" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F38" s="42" t="inlineStr">
+      <c r="I37" s="43" t="inlineStr">
+        <is>
+          <t>06057539</t>
+        </is>
+      </c>
+      <c r="J37" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K37" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L37" s="43" t="n"/>
+      <c r="M37" s="36" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="28">
+      <c r="A38" s="35" t="n"/>
+      <c r="B38" s="44" t="n"/>
+      <c r="C38" s="44" t="n"/>
+      <c r="D38" s="45" t="n"/>
+      <c r="E38" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F38" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 14:00</t>
         </is>
       </c>
-      <c r="G38" s="42" t="inlineStr">
+      <c r="G38" s="43" t="inlineStr">
         <is>
           <t>P-110788</t>
         </is>
       </c>
-      <c r="H38" s="42" t="inlineStr">
+      <c r="H38" s="43" t="inlineStr">
         <is>
           <t>Bijoux BIANGO</t>
         </is>
       </c>
-      <c r="I38" s="42" t="inlineStr">
+      <c r="I38" s="43" t="inlineStr">
         <is>
           <t>0753452871</t>
         </is>
       </c>
-      <c r="J38" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K38" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L38" s="42" t="inlineStr">
+      <c r="J38" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K38" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L38" s="43" t="inlineStr">
         <is>
           <t>Accompagnée de son mari  NKEMA Chicha , qui souhaite s'inscrire également donc 2 rdv en 1</t>
         </is>
       </c>
-      <c r="M38" s="35" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="27">
-      <c r="A39" s="34" t="n"/>
-      <c r="B39" s="43" t="n"/>
-      <c r="C39" s="43" t="n"/>
-      <c r="D39" s="44" t="n"/>
-      <c r="E39" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F39" s="42" t="inlineStr">
+      <c r="M38" s="36" t="n"/>
+      <c r="Z38" s="27" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="28">
+      <c r="A39" s="35" t="n"/>
+      <c r="B39" s="44" t="n"/>
+      <c r="C39" s="44" t="n"/>
+      <c r="D39" s="45" t="n"/>
+      <c r="E39" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F39" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 14:30</t>
         </is>
       </c>
-      <c r="G39" s="42" t="inlineStr">
+      <c r="G39" s="43" t="inlineStr">
         <is>
           <t>P-110894</t>
         </is>
       </c>
-      <c r="H39" s="42" t="inlineStr">
+      <c r="H39" s="43" t="inlineStr">
         <is>
           <t>Moncef NOUASRIA</t>
         </is>
       </c>
-      <c r="I39" s="42" t="inlineStr">
+      <c r="I39" s="43" t="inlineStr">
         <is>
           <t>0622838485</t>
         </is>
       </c>
-      <c r="J39" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K39" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L39" s="42" t="n"/>
-      <c r="M39" s="35" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="27">
-      <c r="A40" s="34" t="n"/>
-      <c r="B40" s="43" t="n"/>
-      <c r="C40" s="43" t="n"/>
-      <c r="D40" s="44" t="n"/>
-      <c r="E40" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F40" s="42" t="inlineStr">
+      <c r="J39" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K39" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L39" s="43" t="n"/>
+      <c r="M39" s="36" t="n"/>
+      <c r="Z39" s="27" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="28">
+      <c r="A40" s="35" t="n"/>
+      <c r="B40" s="44" t="n"/>
+      <c r="C40" s="44" t="n"/>
+      <c r="D40" s="45" t="n"/>
+      <c r="E40" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F40" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 15:00</t>
         </is>
       </c>
-      <c r="G40" s="42" t="inlineStr">
+      <c r="G40" s="43" t="inlineStr">
         <is>
           <t>P-109591</t>
         </is>
       </c>
-      <c r="H40" s="42" t="inlineStr">
+      <c r="H40" s="43" t="inlineStr">
         <is>
           <t>Naima DOUICHI</t>
         </is>
       </c>
-      <c r="I40" s="42" t="inlineStr">
+      <c r="I40" s="43" t="inlineStr">
         <is>
           <t>0626840582</t>
         </is>
       </c>
-      <c r="J40" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K40" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L40" s="42" t="n"/>
-      <c r="M40" s="35" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="27">
-      <c r="A41" s="34" t="n"/>
-      <c r="B41" s="43" t="n"/>
-      <c r="C41" s="43" t="n"/>
-      <c r="D41" s="44" t="n"/>
-      <c r="E41" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F41" s="42" t="inlineStr">
+      <c r="J40" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K40" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L40" s="43" t="n"/>
+      <c r="M40" s="36" t="n"/>
+      <c r="Z40" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="28">
+      <c r="A41" s="35" t="n"/>
+      <c r="B41" s="44" t="n"/>
+      <c r="C41" s="44" t="n"/>
+      <c r="D41" s="45" t="n"/>
+      <c r="E41" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F41" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 15:30</t>
         </is>
       </c>
-      <c r="G41" s="42" t="inlineStr">
+      <c r="G41" s="43" t="inlineStr">
         <is>
           <t>P-108962</t>
         </is>
       </c>
-      <c r="H41" s="42" t="inlineStr">
+      <c r="H41" s="43" t="inlineStr">
         <is>
           <t>M'Barek BADINE</t>
         </is>
       </c>
-      <c r="I41" s="42" t="inlineStr">
+      <c r="I41" s="43" t="inlineStr">
         <is>
           <t>0676573755</t>
         </is>
       </c>
-      <c r="J41" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K41" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L41" s="42" t="n"/>
-      <c r="M41" s="35" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="27">
-      <c r="A42" s="34" t="n"/>
-      <c r="B42" s="43" t="n"/>
-      <c r="C42" s="43" t="n"/>
-      <c r="D42" s="44" t="n"/>
-      <c r="E42" s="42" t="inlineStr">
+      <c r="J41" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K41" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L41" s="43" t="n"/>
+      <c r="M41" s="36" t="n"/>
+      <c r="Z41" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="28">
+      <c r="A42" s="35" t="n"/>
+      <c r="B42" s="44" t="n"/>
+      <c r="C42" s="44" t="n"/>
+      <c r="D42" s="45" t="n"/>
+      <c r="E42" s="43" t="inlineStr">
         <is>
           <t>Vente</t>
         </is>
       </c>
-      <c r="F42" s="42" t="inlineStr">
+      <c r="F42" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 16:00</t>
         </is>
       </c>
-      <c r="G42" s="42" t="inlineStr">
+      <c r="G42" s="43" t="inlineStr">
         <is>
           <t>P-108796</t>
         </is>
       </c>
-      <c r="H42" s="42" t="inlineStr">
+      <c r="H42" s="43" t="inlineStr">
         <is>
           <t>Hassiba BARHOUMI</t>
         </is>
       </c>
-      <c r="I42" s="42" t="inlineStr">
+      <c r="I42" s="43" t="inlineStr">
         <is>
           <t>0751021724</t>
         </is>
       </c>
-      <c r="J42" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K42" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L42" s="42" t="n"/>
-      <c r="M42" s="35" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="27">
-      <c r="A43" s="34" t="n"/>
-      <c r="B43" s="43" t="n"/>
-      <c r="C43" s="43" t="n"/>
-      <c r="D43" s="44" t="n"/>
-      <c r="E43" s="42" t="inlineStr">
-        <is>
-          <t>Inscription</t>
-        </is>
-      </c>
-      <c r="F43" s="42" t="inlineStr">
+      <c r="J42" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K42" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L42" s="43" t="n"/>
+      <c r="M42" s="36" t="n"/>
+      <c r="Z42" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="28">
+      <c r="A43" s="35" t="n"/>
+      <c r="B43" s="44" t="n"/>
+      <c r="C43" s="44" t="n"/>
+      <c r="D43" s="45" t="n"/>
+      <c r="E43" s="43" t="inlineStr">
+        <is>
+          <t>Inscription</t>
+        </is>
+      </c>
+      <c r="F43" s="43" t="inlineStr">
         <is>
           <t>19/10/2023 16:30</t>
         </is>
       </c>
-      <c r="G43" s="42" t="inlineStr">
+      <c r="G43" s="43" t="inlineStr">
         <is>
           <t>P-110902</t>
         </is>
       </c>
-      <c r="H43" s="42" t="inlineStr">
+      <c r="H43" s="43" t="inlineStr">
         <is>
           <t>Gheorghe AVRAM</t>
         </is>
       </c>
-      <c r="I43" s="42" t="inlineStr">
+      <c r="I43" s="43" t="inlineStr">
         <is>
           <t>0472388338</t>
         </is>
       </c>
-      <c r="J43" s="42">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="K43" s="42" t="inlineStr">
-        <is>
-          <t>Inscrit·e</t>
-        </is>
-      </c>
-      <c r="L43" s="42" t="n"/>
-      <c r="M43" s="35" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="27">
-      <c r="A44" s="34" t="n"/>
-      <c r="B44" s="45" t="inlineStr">
+      <c r="J43" s="43">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="K43" s="43" t="inlineStr">
+        <is>
+          <t>Inscrit·e</t>
+        </is>
+      </c>
+      <c r="L43" s="43" t="n"/>
+      <c r="M43" s="36" t="n"/>
+      <c r="Z43" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="28">
+      <c r="A44" s="35" t="n"/>
+      <c r="B44" s="46" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C44" s="46" t="n"/>
-      <c r="D44" s="47" t="inlineStr">
+      <c r="C44" s="47" t="n"/>
+      <c r="D44" s="48" t="inlineStr">
         <is>
           <t>Somme</t>
         </is>
       </c>
-      <c r="E44" s="47" t="n"/>
-      <c r="F44" s="47" t="n"/>
-      <c r="G44" s="47" t="n"/>
-      <c r="H44" s="47" t="n"/>
-      <c r="I44" s="47" t="n"/>
-      <c r="J44" s="48" t="n">
+      <c r="E44" s="48" t="n"/>
+      <c r="F44" s="48" t="n"/>
+      <c r="G44" s="48" t="n"/>
+      <c r="H44" s="48" t="n"/>
+      <c r="I44" s="48" t="n"/>
+      <c r="J44" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="K44" s="48" t="n"/>
-      <c r="L44" s="48" t="n"/>
-      <c r="M44" s="35" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="27">
-      <c r="A45" s="34" t="n"/>
-      <c r="B45" s="49" t="n"/>
-      <c r="C45" s="50" t="n"/>
-      <c r="D45" s="47" t="inlineStr">
+      <c r="K44" s="49" t="n"/>
+      <c r="L44" s="49" t="n"/>
+      <c r="M44" s="36" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="28">
+      <c r="A45" s="35" t="n"/>
+      <c r="B45" s="50" t="n"/>
+      <c r="C45" s="51" t="n"/>
+      <c r="D45" s="48" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="E45" s="48" t="n">
+      <c r="E45" s="49" t="n">
         <v>31</v>
       </c>
-      <c r="F45" s="48" t="n"/>
-      <c r="G45" s="48" t="n"/>
-      <c r="H45" s="48" t="n"/>
-      <c r="I45" s="48" t="n"/>
-      <c r="J45" s="48" t="n"/>
-      <c r="K45" s="48" t="n"/>
-      <c r="L45" s="48" t="n"/>
-      <c r="M45" s="35" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="27">
-      <c r="A46" s="51" t="n"/>
-      <c r="B46" s="51" t="n"/>
-      <c r="C46" s="51" t="n"/>
-      <c r="D46" s="51" t="n"/>
-      <c r="E46" s="51" t="n"/>
-      <c r="F46" s="51" t="n"/>
-      <c r="G46" s="51" t="n"/>
-      <c r="H46" s="51" t="n"/>
-      <c r="I46" s="51" t="n"/>
-      <c r="J46" s="51" t="n"/>
-      <c r="K46" s="51" t="n"/>
-      <c r="L46" s="51" t="n"/>
-      <c r="M46" s="52" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="27">
-      <c r="A47" s="51" t="n"/>
-      <c r="B47" s="51" t="n"/>
-      <c r="C47" s="51" t="n"/>
-      <c r="D47" s="51" t="n"/>
-      <c r="E47" s="51" t="n"/>
-      <c r="F47" s="51" t="n"/>
-      <c r="G47" s="51" t="n"/>
-      <c r="H47" s="51" t="n"/>
-      <c r="I47" s="51" t="n"/>
-      <c r="J47" s="51" t="n"/>
-      <c r="K47" s="51" t="n"/>
-      <c r="L47" s="51" t="n"/>
-      <c r="M47" s="52" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="27">
-      <c r="A48" s="51" t="n"/>
-      <c r="B48" s="51" t="inlineStr">
+      <c r="F45" s="49" t="n"/>
+      <c r="G45" s="49" t="n"/>
+      <c r="H45" s="49" t="n"/>
+      <c r="I45" s="49" t="n"/>
+      <c r="J45" s="49" t="n"/>
+      <c r="K45" s="49" t="n"/>
+      <c r="L45" s="49" t="n"/>
+      <c r="M45" s="36" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="28">
+      <c r="A46" s="52" t="n"/>
+      <c r="B46" s="52" t="n"/>
+      <c r="C46" s="52" t="n"/>
+      <c r="D46" s="52" t="n"/>
+      <c r="E46" s="52" t="n"/>
+      <c r="F46" s="52" t="n"/>
+      <c r="G46" s="52" t="n"/>
+      <c r="H46" s="52" t="n"/>
+      <c r="I46" s="52" t="n"/>
+      <c r="J46" s="52" t="n"/>
+      <c r="K46" s="52" t="n"/>
+      <c r="L46" s="52" t="n"/>
+      <c r="M46" s="53" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="28">
+      <c r="A47" s="52" t="n"/>
+      <c r="B47" s="52" t="n"/>
+      <c r="C47" s="52" t="n"/>
+      <c r="D47" s="52" t="n"/>
+      <c r="E47" s="52" t="n"/>
+      <c r="F47" s="52" t="n"/>
+      <c r="G47" s="52" t="n"/>
+      <c r="H47" s="52" t="n"/>
+      <c r="I47" s="52" t="n"/>
+      <c r="J47" s="52" t="n"/>
+      <c r="K47" s="52" t="n"/>
+      <c r="L47" s="52" t="n"/>
+      <c r="M47" s="53" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="28">
+      <c r="A48" s="52" t="n"/>
+      <c r="B48" s="52" t="inlineStr">
         <is>
           <t>Informations confidentielles - Ne pas distribuer</t>
         </is>
       </c>
-      <c r="C48" s="51" t="n"/>
-      <c r="D48" s="51" t="n"/>
-      <c r="E48" s="51" t="n"/>
-      <c r="F48" s="51" t="n"/>
-      <c r="G48" s="51" t="n"/>
-      <c r="H48" s="51" t="n"/>
-      <c r="I48" s="51" t="n"/>
-      <c r="J48" s="51" t="n"/>
-      <c r="K48" s="51" t="n"/>
-      <c r="L48" s="51" t="n"/>
-      <c r="M48" s="52" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="27">
-      <c r="A49" s="53" t="n"/>
-      <c r="B49" s="53" t="inlineStr">
+      <c r="C48" s="52" t="n"/>
+      <c r="D48" s="52" t="n"/>
+      <c r="E48" s="52" t="n"/>
+      <c r="F48" s="52" t="n"/>
+      <c r="G48" s="52" t="n"/>
+      <c r="H48" s="52" t="n"/>
+      <c r="I48" s="52" t="n"/>
+      <c r="J48" s="52" t="n"/>
+      <c r="K48" s="52" t="n"/>
+      <c r="L48" s="52" t="n"/>
+      <c r="M48" s="53" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="28">
+      <c r="A49" s="54" t="n"/>
+      <c r="B49" s="54" t="inlineStr">
         <is>
           <t>Copyright © 2000-2023 salesforce.com, inc. Tous droits réservés.</t>
         </is>
       </c>
-      <c r="C49" s="53" t="n"/>
-      <c r="D49" s="53" t="n"/>
-      <c r="E49" s="53" t="n"/>
-      <c r="F49" s="53" t="n"/>
-      <c r="G49" s="53" t="n"/>
-      <c r="H49" s="53" t="n"/>
-      <c r="I49" s="53" t="n"/>
-      <c r="J49" s="53" t="n"/>
-      <c r="K49" s="53" t="n"/>
-      <c r="L49" s="53" t="n"/>
-      <c r="M49" s="54" t="n"/>
+      <c r="C49" s="54" t="n"/>
+      <c r="D49" s="54" t="n"/>
+      <c r="E49" s="54" t="n"/>
+      <c r="F49" s="54" t="n"/>
+      <c r="G49" s="54" t="n"/>
+      <c r="H49" s="54" t="n"/>
+      <c r="I49" s="54" t="n"/>
+      <c r="J49" s="54" t="n"/>
+      <c r="K49" s="54" t="n"/>
+      <c r="L49" s="54" t="n"/>
+      <c r="M49" s="55" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="32">
